--- a/labs/lab-06-reconcile-accounts-and-forecast-with-copilot/northstar-reconciliation-forecast-starter.xlsx
+++ b/labs/lab-06-reconcile-accounts-and-forecast-with-copilot/northstar-reconciliation-forecast-starter.xlsx
@@ -28,7 +28,7 @@
     <t>Course</t>
   </si>
   <si>
-    <t>Generative AI for Finance and Fintech (TGS-2026065050)</t>
+    <t>Microsoft Copilot for Finance (TGS-2026065050)</t>
   </si>
   <si>
     <t>TSC mapping</t>
